--- a/data/processed/positivacao/2021-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2021-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24555,7 +24555,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B932" t="inlineStr"/>
@@ -36323,7 +36323,7 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr"/>
@@ -65085,7 +65085,7 @@
     <row r="2492">
       <c r="A2492" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2492" t="inlineStr"/>
@@ -66730,12 +66730,12 @@
       <c r="A2556" t="inlineStr"/>
       <c r="B2556" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 75 cliente(s), não positivou 756 cliente(s) - Total vendido: R$ 77.152,28
-Vendedor 3 - FERNANDA: positivou 99 cliente(s), não positivou 353 cliente(s) - Total vendido: R$ 84.702,63
-Vendedor 4 - DANIELA: positivou 1 cliente(s), não positivou 645 cliente(s) - Total vendido: R$ 92,72
+Vendedor 3 - VENDEDOR 03: positivou 99 cliente(s), não positivou 353 cliente(s) - Total vendido: R$ 84.702,63
+Vendedor 4 - VENDEDOR 04: positivou 1 cliente(s), não positivou 645 cliente(s) - Total vendido: R$ 92,72
 Vendedor 5 - SITE: positivou 17 cliente(s), não positivou 442 cliente(s) - Total vendido: R$ 1.197,92
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2556" t="inlineStr"/>
